--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02BF0BD-BBE6-44C3-8CAB-1BD1B1A1C75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09058C93-170A-4358-A551-07EB187C3742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -289,9 +289,6 @@
     <t>tsg y flow a ajustar - repetimos montos</t>
   </si>
   <si>
-    <t>CERRRAJERIA - ARREGLO CERRADURA PUERTA PRINCIPAL</t>
-  </si>
-  <si>
     <t>Vto. 16/06</t>
   </si>
   <si>
@@ -299,6 +296,9 @@
   </si>
   <si>
     <t>TSG - MES DE MAYO</t>
+  </si>
+  <si>
+    <t>CERRRAJERIA - ARREGLO CERRADURA PORTON</t>
   </si>
 </sst>
 </file>
@@ -1489,6 +1489,8 @@
     <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1567,8 +1569,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1937,22 +1937,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1960,27 +1960,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1988,13 +1988,13 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2002,24 +2002,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="139" t="s">
+      <c r="E11" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="139"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="141"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
@@ -2035,11 +2035,11 @@
         <v>-1387513.66056</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="169">
+      <c r="C13" s="139">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2051,7 +2051,7 @@
         <v>380193.28760000004</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
@@ -2067,14 +2067,14 @@
       </c>
       <c r="F14" s="59">
         <f>-(C37)</f>
-        <v>-398872.64999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-378872.64999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="170">
+      <c r="C15" s="140">
         <v>8062.99</v>
       </c>
       <c r="D15" s="5"/>
@@ -2086,7 +2086,7 @@
         <v>-538257.21</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
@@ -2102,16 +2102,16 @@
         <v>491608.95800000004</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="31"/>
       <c r="C17" s="113"/>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="113">
         <v>12287</v>
@@ -2120,7 +2120,7 @@
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31"/>
       <c r="C19" s="80"/>
       <c r="E19" s="58"/>
@@ -2129,7 +2129,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20" s="87">
@@ -2141,10 +2141,10 @@
       </c>
       <c r="F20" s="122">
         <f>SUM(F12:F19)</f>
-        <v>-1452841.2749599998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-1432841.2749599998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>66</v>
       </c>
@@ -2166,19 +2166,19 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="113">
-        <v>60000</v>
+      <c r="C23" s="140">
+        <v>40000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="31"/>
       <c r="B24" s="35"/>
       <c r="C24" s="113"/>
@@ -2186,7 +2186,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>60</v>
       </c>
@@ -2198,32 +2198,32 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="109">
         <f>SUM(C21:C25)</f>
-        <v>125203.95</v>
+        <v>105203.95</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="55"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="49">
         <f>+C26+C20</f>
-        <v>398872.64999999997</v>
+        <v>378872.64999999997</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="69" t="s">
         <v>24</v>
       </c>
@@ -2232,18 +2232,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
       <c r="B30" s="29"/>
       <c r="C30" s="54"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52"/>
       <c r="B31" s="51"/>
       <c r="C31" s="53">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="61"/>
       <c r="B32" s="62"/>
       <c r="C32" s="53">
@@ -2259,19 +2259,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="78"/>
       <c r="B33" s="79"/>
       <c r="C33" s="81"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
       <c r="B35" s="84"/>
       <c r="C35" s="81">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="63" t="s">
         <v>23</v>
       </c>
@@ -2289,98 +2289,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="53">
         <f>C27-C25</f>
-        <v>398872.64999999997</v>
+        <v>378872.64999999997</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="77">
         <f>+C27</f>
-        <v>398872.64999999997</v>
+        <v>378872.64999999997</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="65">
         <f>+C27+C36</f>
-        <v>398872.64999999997</v>
+        <v>378872.64999999997</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="140"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="140"/>
-      <c r="C47" s="140"/>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="140"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="142"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="142"/>
+      <c r="E46" s="142"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="142"/>
+      <c r="C47" s="142"/>
+      <c r="D47" s="142"/>
+      <c r="E47" s="142"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="142"/>
+      <c r="C48" s="142"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="142"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -2406,25 +2406,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2445,7 +2445,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2465,7 +2465,7 @@
       <c r="L2" s="115"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2540,7 +2540,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>165927.71752960002</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>455932.81111407414</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2813,71 +2813,71 @@
         <v>890295.19488367415</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="141"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="143"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="142"/>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="142"/>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="142"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="142"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="142"/>
-      <c r="I15" s="142"/>
-      <c r="J15" s="142"/>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="142"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="142"/>
-      <c r="H16" s="142"/>
-      <c r="I16" s="142"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="142"/>
-      <c r="L16" s="142"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2896,33 +2896,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1"/>
       <c r="B1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="B2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="B3"/>
       <c r="K3" t="s">
@@ -2933,7 +2933,7 @@
         <v>154256.57</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4" s="125" t="s">
@@ -2960,7 +2960,7 @@
         <v>71763.12000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5" s="33" t="s">
@@ -2971,7 +2971,7 @@
         <v>235242.38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6" s="108" t="s">
@@ -3006,7 +3006,7 @@
         <v>88731.754000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="123"/>
@@ -3040,7 +3040,7 @@
         <v>131973.81400000001</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
       <c r="B8"/>
       <c r="G8">
@@ -3067,7 +3067,7 @@
         <v>96846.073999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9"/>
       <c r="G9" s="126">
@@ -3095,7 +3095,7 @@
         <v>131973.81400000001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10"/>
       <c r="B10"/>
       <c r="G10" s="125">
@@ -3123,7 +3123,7 @@
         <v>88731.754000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="B11"/>
       <c r="L11" s="127">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="N11" s="129"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="B12"/>
       <c r="N12" s="129"/>
     </row>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13" s="133" t="s">
@@ -3155,7 +3155,7 @@
       <c r="M13" s="133"/>
       <c r="N13" s="129"/>
     </row>
-    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
       <c r="B14"/>
       <c r="N14" s="131">
@@ -3163,12 +3163,12 @@
         <v>538257.21</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="120" t="s">
         <v>81</v>
       </c>
@@ -3178,13 +3178,13 @@
       <c r="F17" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="146" t="s">
+      <c r="H17" s="148" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="147"/>
-      <c r="J17" s="148"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I17" s="149"/>
+      <c r="J17" s="150"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="121">
         <v>110347.016</v>
       </c>
@@ -3196,14 +3196,14 @@
         <f>N6</f>
         <v>88731.754000000001</v>
       </c>
-      <c r="H18" s="149">
+      <c r="H18" s="151">
         <f>C18-E18+F18</f>
         <v>88731.754000000001</v>
       </c>
-      <c r="I18" s="150"/>
-      <c r="J18" s="151"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I18" s="152"/>
+      <c r="J18" s="153"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="121">
         <v>160567.91</v>
       </c>
@@ -3212,14 +3212,14 @@
         <f>N7</f>
         <v>131973.81400000001</v>
       </c>
-      <c r="H19" s="149">
+      <c r="H19" s="151">
         <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
         <v>292541.72400000005</v>
       </c>
-      <c r="I19" s="150"/>
-      <c r="J19" s="151"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I19" s="152"/>
+      <c r="J19" s="153"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="121">
         <v>110347.016</v>
       </c>
@@ -3231,14 +3231,14 @@
         <f t="shared" ref="F20:F22" si="3">N8</f>
         <v>96846.073999999993</v>
       </c>
-      <c r="H20" s="149">
+      <c r="H20" s="151">
         <f>C20-E20+F20</f>
         <v>96846.073999999993</v>
       </c>
-      <c r="I20" s="150"/>
-      <c r="J20" s="151"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I20" s="152"/>
+      <c r="J20" s="153"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="121">
         <v>160567.91</v>
       </c>
@@ -3250,14 +3250,14 @@
         <f>N9</f>
         <v>131973.81400000001</v>
       </c>
-      <c r="H21" s="149">
+      <c r="H21" s="151">
         <f t="shared" si="2"/>
         <v>131973.81400000001</v>
       </c>
-      <c r="I21" s="150"/>
-      <c r="J21" s="151"/>
-    </row>
-    <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I21" s="152"/>
+      <c r="J21" s="153"/>
+    </row>
+    <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="121">
         <v>110347.016</v>
       </c>
@@ -3269,14 +3269,14 @@
         <f t="shared" si="3"/>
         <v>88731.754000000001</v>
       </c>
-      <c r="H22" s="143">
+      <c r="H22" s="145">
         <f t="shared" si="2"/>
         <v>88731.754000000001</v>
       </c>
-      <c r="I22" s="144"/>
-      <c r="J22" s="145"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I22" s="146"/>
+      <c r="J22" s="147"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E24" s="6">
         <f>SUM(E18:E23)</f>
         <v>491608.95800000004</v>
@@ -3300,7 +3300,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59F83D-EB65-4E23-8775-704ADF1A523E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3309,68 +3309,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="157" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="159" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="159"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="161"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="160" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="161"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="163">
+      <c r="B2" s="163"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="165">
         <v>565</v>
       </c>
-      <c r="E2" s="164"/>
+      <c r="E2" s="166"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="165" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="165" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="165" t="s">
+      <c r="C3" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="167" t="s">
+      <c r="D3" s="169" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="152" t="s">
+      <c r="E3" s="154" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="152" t="s">
+      <c r="F3" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="152" t="s">
+      <c r="G3" s="154" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="166"/>
-      <c r="B4" s="166"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="168"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="170"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -3527,12 +3527,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="154"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="155"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="156"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="156"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="158"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09058C93-170A-4358-A551-07EB187C3742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA5E30-9238-47BA-B24C-EABDA6378A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
   <si>
     <t>UF</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>CERRRAJERIA - ARREGLO CERRADURA PORTON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferreteria V&amp;A </t>
   </si>
 </sst>
 </file>
@@ -1486,11 +1489,11 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="14" fillId="9" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1937,22 +1940,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1960,27 +1963,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2002,12 +2005,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
@@ -2019,7 +2022,7 @@
       </c>
       <c r="F11" s="141"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
@@ -2035,11 +2038,11 @@
         <v>-1387513.66056</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="139">
+      <c r="C13" s="138">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2051,7 +2054,7 @@
         <v>380193.28760000004</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
@@ -2067,14 +2070,14 @@
       </c>
       <c r="F14" s="59">
         <f>-(C37)</f>
-        <v>-378872.64999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-422380.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="140">
+      <c r="C15" s="139">
         <v>8062.99</v>
       </c>
       <c r="D15" s="5"/>
@@ -2083,15 +2086,15 @@
       </c>
       <c r="F15" s="59">
         <f>-EDESUR!E7</f>
-        <v>-538257.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-562429.18999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="113">
-        <v>47396.4</v>
+      <c r="C16" s="139">
+        <v>70904.02</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58" t="s">
@@ -2102,14 +2105,18 @@
         <v>491608.95800000004</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="C17" s="113"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="139">
+        <v>20000</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
         <v>88</v>
       </c>
@@ -2120,7 +2127,7 @@
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="31"/>
       <c r="C19" s="80"/>
       <c r="E19" s="58"/>
@@ -2129,22 +2136,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>273668.69999999995</v>
+        <v>317176.32000000001</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="122">
         <f>SUM(F12:F19)</f>
-        <v>-1432841.2749599998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-1500520.8749599997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
@@ -2153,7 +2160,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
         <v>66</v>
       </c>
@@ -2166,19 +2173,19 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="140">
+      <c r="C23" s="139">
         <v>40000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="31"/>
       <c r="B24" s="35"/>
       <c r="C24" s="113"/>
@@ -2186,7 +2193,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
         <v>60</v>
       </c>
@@ -2198,7 +2205,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="109">
@@ -2210,20 +2217,20 @@
       <c r="F26" s="55"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="49">
         <f>+C26+C20</f>
-        <v>378872.64999999997</v>
+        <v>422380.27</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="69" t="s">
         <v>24</v>
       </c>
@@ -2232,18 +2239,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44"/>
       <c r="B30" s="29"/>
       <c r="C30" s="54"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52"/>
       <c r="B31" s="51"/>
       <c r="C31" s="53">
@@ -2251,7 +2258,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="61"/>
       <c r="B32" s="62"/>
       <c r="C32" s="53">
@@ -2259,19 +2266,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="78"/>
       <c r="B33" s="79"/>
       <c r="C33" s="81"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="78"/>
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="78"/>
       <c r="B35" s="84"/>
       <c r="C35" s="81">
@@ -2279,7 +2286,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="63" t="s">
         <v>23</v>
       </c>
@@ -2289,98 +2296,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="53">
         <f>C27-C25</f>
-        <v>378872.64999999997</v>
+        <v>422380.27</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="77">
         <f>+C27</f>
-        <v>378872.64999999997</v>
+        <v>422380.27</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="65">
         <f>+C27+C36</f>
-        <v>378872.64999999997</v>
+        <v>422380.27</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B46" s="142"/>
       <c r="C46" s="142"/>
       <c r="D46" s="142"/>
       <c r="E46" s="142"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B47" s="142"/>
       <c r="C47" s="142"/>
       <c r="D47" s="142"/>
       <c r="E47" s="142"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B48" s="142"/>
       <c r="C48" s="142"/>
       <c r="D48" s="142"/>
       <c r="E48" s="142"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -2406,25 +2413,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2445,7 +2452,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2465,7 +2472,7 @@
       <c r="L2" s="115"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2513,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2540,7 +2547,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2586,7 +2593,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2632,7 +2639,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2675,7 +2682,7 @@
         <v>165927.71752960002</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2720,7 +2727,7 @@
         <v>455932.81111407414</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2766,7 +2773,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2813,7 +2820,7 @@
         <v>890295.19488367415</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="143"/>
       <c r="B11" s="143"/>
       <c r="C11" s="143"/>
@@ -2828,10 +2835,10 @@
       <c r="L11" s="143"/>
       <c r="M11" s="143"/>
     </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C13" s="144"/>
       <c r="D13" s="144"/>
       <c r="E13" s="144"/>
@@ -2843,7 +2850,7 @@
       <c r="K13" s="144"/>
       <c r="L13" s="144"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" s="144"/>
       <c r="D14" s="144"/>
       <c r="E14" s="144"/>
@@ -2855,7 +2862,7 @@
       <c r="K14" s="144"/>
       <c r="L14" s="144"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" s="144"/>
       <c r="D15" s="144"/>
       <c r="E15" s="144"/>
@@ -2867,7 +2874,7 @@
       <c r="K15" s="144"/>
       <c r="L15" s="144"/>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="144"/>
       <c r="D16" s="144"/>
       <c r="E16" s="144"/>
@@ -2896,33 +2903,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1"/>
       <c r="B1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2"/>
       <c r="B2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3"/>
       <c r="K3" t="s">
@@ -2933,15 +2940,15 @@
         <v>154256.57</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4" s="125" t="s">
         <v>73</v>
       </c>
       <c r="D4" s="125"/>
-      <c r="E4" s="136">
-        <v>148758.26</v>
+      <c r="E4" s="140">
+        <v>172930.24</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -2960,25 +2967,25 @@
         <v>71763.12000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5" s="33" t="s">
         <v>74</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="137">
+      <c r="E5" s="136">
         <v>235242.38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6" s="108" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="108"/>
-      <c r="E6" s="138">
+      <c r="E6" s="137">
         <v>154256.57</v>
       </c>
       <c r="G6" s="125">
@@ -2995,7 +3002,7 @@
       </c>
       <c r="K6" s="121">
         <f>E4/2</f>
-        <v>74379.13</v>
+        <v>86465.12</v>
       </c>
       <c r="L6" s="127">
         <f>O$4/5</f>
@@ -3003,17 +3010,17 @@
       </c>
       <c r="N6" s="128">
         <f>SUM(K6:M6)</f>
-        <v>88731.754000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>100817.74399999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="123"/>
       <c r="D7" s="123"/>
       <c r="E7" s="124">
         <f>SUM(E4:E6)</f>
-        <v>538257.21</v>
+        <v>562429.18999999994</v>
       </c>
       <c r="G7" s="126">
         <v>2</v>
@@ -3040,7 +3047,7 @@
         <v>131973.81400000001</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="G8">
@@ -3067,7 +3074,7 @@
         <v>96846.073999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9"/>
       <c r="B9"/>
       <c r="G9" s="126">
@@ -3095,7 +3102,7 @@
         <v>131973.81400000001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10"/>
       <c r="B10"/>
       <c r="G10" s="125">
@@ -3112,7 +3119,7 @@
       </c>
       <c r="K10" s="121">
         <f>E4/2</f>
-        <v>74379.13</v>
+        <v>86465.12</v>
       </c>
       <c r="L10" s="127">
         <f t="shared" si="1"/>
@@ -3120,10 +3127,10 @@
       </c>
       <c r="N10" s="130">
         <f t="shared" si="0"/>
-        <v>88731.754000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100817.74399999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11"/>
       <c r="B11"/>
       <c r="L11" s="127">
@@ -3132,12 +3139,12 @@
       </c>
       <c r="N11" s="129"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12"/>
       <c r="B12"/>
       <c r="N12" s="129"/>
     </row>
-    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13" s="133" t="s">
@@ -3155,20 +3162,20 @@
       <c r="M13" s="133"/>
       <c r="N13" s="129"/>
     </row>
-    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14"/>
       <c r="B14"/>
       <c r="N14" s="131">
         <f>SUM(N6:N13)</f>
-        <v>538257.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>562429.18999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="120" t="s">
         <v>81</v>
       </c>
@@ -3184,7 +3191,7 @@
       <c r="I17" s="149"/>
       <c r="J17" s="150"/>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="121">
         <v>110347.016</v>
       </c>
@@ -3194,16 +3201,16 @@
       </c>
       <c r="F18" s="6">
         <f>N6</f>
-        <v>88731.754000000001</v>
+        <v>100817.74399999999</v>
       </c>
       <c r="H18" s="151">
         <f>C18-E18+F18</f>
-        <v>88731.754000000001</v>
+        <v>100817.74399999999</v>
       </c>
       <c r="I18" s="152"/>
       <c r="J18" s="153"/>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="121">
         <v>160567.91</v>
       </c>
@@ -3219,7 +3226,7 @@
       <c r="I19" s="152"/>
       <c r="J19" s="153"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="121">
         <v>110347.016</v>
       </c>
@@ -3238,7 +3245,7 @@
       <c r="I20" s="152"/>
       <c r="J20" s="153"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="121">
         <v>160567.91</v>
       </c>
@@ -3257,7 +3264,7 @@
       <c r="I21" s="152"/>
       <c r="J21" s="153"/>
     </row>
-    <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="121">
         <v>110347.016</v>
       </c>
@@ -3267,16 +3274,16 @@
       </c>
       <c r="F22" s="6">
         <f t="shared" si="3"/>
-        <v>88731.754000000001</v>
+        <v>100817.74399999999</v>
       </c>
       <c r="H22" s="145">
         <f t="shared" si="2"/>
-        <v>88731.754000000001</v>
+        <v>100817.74399999999</v>
       </c>
       <c r="I22" s="146"/>
       <c r="J22" s="147"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E24" s="6">
         <f>SUM(E18:E23)</f>
         <v>491608.95800000004</v>
@@ -3300,7 +3307,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59F83D-EB65-4E23-8775-704ADF1A523E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3309,12 +3316,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="159" t="s">
         <v>24</v>
       </c>
@@ -3325,7 +3332,7 @@
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="162" t="s">
         <v>50</v>
       </c>
@@ -3338,7 +3345,7 @@
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="167" t="s">
         <v>0</v>
       </c>
@@ -3361,7 +3368,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="168"/>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -3370,7 +3377,7 @@
       <c r="F4" s="155"/>
       <c r="G4" s="155"/>
     </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -3393,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -3416,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -3439,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -3462,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -3485,7 +3492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -3508,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -3527,7 +3534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="156"/>
       <c r="B12" s="157"/>
       <c r="C12" s="157"/>

--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA5E30-9238-47BA-B24C-EABDA6378A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FC14F8-3B75-49FD-943A-9F7058FB1DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1489,7 +1489,6 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="14" fillId="9" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1572,6 +1571,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2017,10 +2017,10 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="141" t="s">
+      <c r="E11" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="141"/>
+      <c r="F11" s="140"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="107" t="s">
@@ -2042,7 +2042,7 @@
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="138">
+      <c r="C13" s="137">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2077,7 +2077,7 @@
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="139">
+      <c r="C15" s="138">
         <v>8062.99</v>
       </c>
       <c r="D15" s="5"/>
@@ -2086,14 +2086,14 @@
       </c>
       <c r="F15" s="59">
         <f>-EDESUR!E7</f>
-        <v>-562429.18999999994</v>
+        <v>-374776.3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="139">
+      <c r="C16" s="138">
         <v>70904.02</v>
       </c>
       <c r="D16" s="5"/>
@@ -2109,7 +2109,7 @@
       <c r="A17" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="139">
+      <c r="C17" s="138">
         <v>20000</v>
       </c>
       <c r="D17" s="5"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="F20" s="122">
         <f>SUM(F12:F19)</f>
-        <v>-1500520.8749599997</v>
+        <v>-1312867.9849599998</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2178,7 +2178,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="139">
+      <c r="C23" s="138">
         <v>40000</v>
       </c>
       <c r="D23" s="5"/>
@@ -2335,22 +2335,22 @@
       <c r="E45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="142"/>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
+      <c r="B46" s="141"/>
+      <c r="C46" s="141"/>
+      <c r="D46" s="141"/>
+      <c r="E46" s="141"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="142"/>
-      <c r="C47" s="142"/>
-      <c r="D47" s="142"/>
-      <c r="E47" s="142"/>
+      <c r="B47" s="141"/>
+      <c r="C47" s="141"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="141"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="142"/>
-      <c r="C48" s="142"/>
-      <c r="D48" s="142"/>
-      <c r="E48" s="142"/>
+      <c r="B48" s="141"/>
+      <c r="C48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="19"/>
@@ -2821,70 +2821,70 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="143"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
-      <c r="E11" s="143"/>
-      <c r="F11" s="143"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="143"/>
-      <c r="M11" s="143"/>
+      <c r="A11" s="142"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2947,7 +2947,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="125"/>
-      <c r="E4" s="140">
+      <c r="E4" s="139">
         <v>172930.24</v>
       </c>
       <c r="G4" t="s">
@@ -2974,8 +2974,8 @@
         <v>74</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="136">
-        <v>235242.38</v>
+      <c r="E5" s="170">
+        <v>47589.49</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2985,7 +2985,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="108"/>
-      <c r="E6" s="137">
+      <c r="E6" s="136">
         <v>154256.57</v>
       </c>
       <c r="G6" s="125">
@@ -3020,7 +3020,7 @@
       <c r="D7" s="123"/>
       <c r="E7" s="124">
         <f>SUM(E4:E6)</f>
-        <v>562429.18999999994</v>
+        <v>374776.3</v>
       </c>
       <c r="G7" s="126">
         <v>2</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K7" s="121">
         <f>E5/2</f>
-        <v>117621.19</v>
+        <v>23794.744999999999</v>
       </c>
       <c r="L7" s="127">
         <f>O$4/5</f>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="N7" s="134">
         <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
-        <v>131973.81400000001</v>
+        <v>38147.368999999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="K9" s="121">
         <f>E5/2</f>
-        <v>117621.19</v>
+        <v>23794.744999999999</v>
       </c>
       <c r="L9" s="127">
         <f t="shared" si="1"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="N9" s="134">
         <f t="shared" si="0"/>
-        <v>131973.81400000001</v>
+        <v>38147.368999999999</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3167,7 +3167,7 @@
       <c r="B14"/>
       <c r="N14" s="131">
         <f>SUM(N6:N13)</f>
-        <v>562429.18999999994</v>
+        <v>374776.3</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -3185,11 +3185,11 @@
       <c r="F17" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="148" t="s">
+      <c r="H17" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="149"/>
-      <c r="J17" s="150"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="149"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="121">
@@ -3203,12 +3203,12 @@
         <f>N6</f>
         <v>100817.74399999999</v>
       </c>
-      <c r="H18" s="151">
+      <c r="H18" s="150">
         <f>C18-E18+F18</f>
         <v>100817.74399999999</v>
       </c>
-      <c r="I18" s="152"/>
-      <c r="J18" s="153"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="152"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="121">
@@ -3217,14 +3217,14 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6">
         <f>N7</f>
-        <v>131973.81400000001</v>
-      </c>
-      <c r="H19" s="151">
+        <v>38147.368999999999</v>
+      </c>
+      <c r="H19" s="150">
         <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
-        <v>292541.72400000005</v>
-      </c>
-      <c r="I19" s="152"/>
-      <c r="J19" s="153"/>
+        <v>198715.27900000001</v>
+      </c>
+      <c r="I19" s="151"/>
+      <c r="J19" s="152"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="121">
@@ -3238,12 +3238,12 @@
         <f t="shared" ref="F20:F22" si="3">N8</f>
         <v>96846.073999999993</v>
       </c>
-      <c r="H20" s="151">
+      <c r="H20" s="150">
         <f>C20-E20+F20</f>
         <v>96846.073999999993</v>
       </c>
-      <c r="I20" s="152"/>
-      <c r="J20" s="153"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="152"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="121">
@@ -3255,14 +3255,14 @@
       </c>
       <c r="F21" s="6">
         <f>N9</f>
-        <v>131973.81400000001</v>
-      </c>
-      <c r="H21" s="151">
+        <v>38147.368999999999</v>
+      </c>
+      <c r="H21" s="150">
         <f t="shared" si="2"/>
-        <v>131973.81400000001</v>
-      </c>
-      <c r="I21" s="152"/>
-      <c r="J21" s="153"/>
+        <v>38147.368999999999</v>
+      </c>
+      <c r="I21" s="151"/>
+      <c r="J21" s="152"/>
     </row>
     <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="121">
@@ -3276,12 +3276,12 @@
         <f t="shared" si="3"/>
         <v>100817.74399999999</v>
       </c>
-      <c r="H22" s="145">
+      <c r="H22" s="144">
         <f t="shared" si="2"/>
         <v>100817.74399999999</v>
       </c>
-      <c r="I22" s="146"/>
-      <c r="J22" s="147"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="146"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="E24" s="6">
@@ -3322,60 +3322,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="158" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="161"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="160"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="161" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="165">
+      <c r="B2" s="162"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="164">
         <v>565</v>
       </c>
-      <c r="E2" s="166"/>
+      <c r="E2" s="165"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="167" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="167" t="s">
+      <c r="A3" s="166" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="169" t="s">
+      <c r="D3" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="154" t="s">
+      <c r="E3" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="154" t="s">
+      <c r="F3" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="154" t="s">
+      <c r="G3" s="153" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="168"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="168"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="90">
@@ -3535,11 +3535,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="156"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="158"/>
+      <c r="A12" s="155"/>
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="157"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FC14F8-3B75-49FD-943A-9F7058FB1DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F71CE4-17A0-40B9-AD22-2FC5EE1F4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>UF</t>
   </si>
@@ -301,7 +301,10 @@
     <t>CERRRAJERIA - ARREGLO CERRADURA PORTON</t>
   </si>
   <si>
-    <t xml:space="preserve">ferreteria V&amp;A </t>
+    <t>SALVATIERRA MATIAS - DESOBSTRUCCION COLECTORA CLOACAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRETERIA V&amp;A </t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1271,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1458,7 +1461,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1488,11 +1490,10 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="14" fillId="9" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1571,7 +1572,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1940,22 +1945,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1963,27 +1968,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1997,7 +2002,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2005,29 +2010,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="140" t="s">
+      <c r="E11" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="140"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="138"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="135">
+      <c r="C12" s="169">
         <v>80236.31</v>
       </c>
       <c r="D12" s="5"/>
@@ -2035,14 +2040,15 @@
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-1387513.66056</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-1484152</f>
+        <v>-1484152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="134">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2051,17 +2057,17 @@
       </c>
       <c r="F13" s="59">
         <f>'prorrateo '!F10</f>
-        <v>380193.28760000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>172073.50400000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="80">
+      <c r="C14" s="172">
         <v>33600</v>
       </c>
       <c r="D14" s="5"/>
@@ -2070,15 +2076,15 @@
       </c>
       <c r="F14" s="59">
         <f>-(C37)</f>
-        <v>-422380.27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-513425.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="138">
-        <v>8062.99</v>
+      <c r="C15" s="135">
+        <v>39299</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="58" t="s">
@@ -2086,14 +2092,14 @@
       </c>
       <c r="F15" s="59">
         <f>-EDESUR!E7</f>
-        <v>-374776.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-205464.27000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="138">
+      <c r="C16" s="135">
         <v>70904.02</v>
       </c>
       <c r="D16" s="5"/>
@@ -2102,98 +2108,102 @@
       </c>
       <c r="F16" s="59">
         <f>EDESUR!E24</f>
-        <v>491608.95800000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>220705.56800000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="138">
+        <v>91</v>
+      </c>
+      <c r="C17" s="135">
         <v>20000</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="113">
+      <c r="C18" s="168">
         <v>12287</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31"/>
       <c r="C19" s="80"/>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
-      <c r="H19" s="123" t="s">
+      <c r="H19" s="122" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>317176.32000000001</v>
+        <v>348412.33</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="122">
+      <c r="F20" s="121">
         <f>SUM(F12:F19)</f>
-        <v>-1312867.9849599998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-1810262.6780000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="114"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>66</v>
       </c>
       <c r="B22" s="35"/>
-      <c r="C22" s="113">
-        <f>62099*5%+62099</f>
-        <v>65203.95</v>
+      <c r="C22" s="135">
+        <f>65203*5%+65203</f>
+        <v>68463.149999999994</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="138">
+      <c r="C23" s="135">
         <v>40000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>90</v>
+      </c>
       <c r="B24" s="35"/>
-      <c r="C24" s="113"/>
+      <c r="C24" s="135">
+        <v>56550</v>
+      </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>60</v>
       </c>
@@ -2205,32 +2215,32 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="109">
         <f>SUM(C21:C25)</f>
-        <v>105203.95</v>
+        <v>165013.15</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="55"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="49">
         <f>+C26+C20</f>
-        <v>422380.27</v>
+        <v>513425.48</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="69" t="s">
         <v>24</v>
       </c>
@@ -2239,18 +2249,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
       <c r="B30" s="29"/>
       <c r="C30" s="54"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52"/>
       <c r="B31" s="51"/>
       <c r="C31" s="53">
@@ -2258,7 +2268,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="61"/>
       <c r="B32" s="62"/>
       <c r="C32" s="53">
@@ -2266,19 +2276,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="78"/>
       <c r="B33" s="79"/>
       <c r="C33" s="81"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
       <c r="B35" s="84"/>
       <c r="C35" s="81">
@@ -2286,7 +2296,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="63" t="s">
         <v>23</v>
       </c>
@@ -2296,98 +2306,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="53">
         <f>C27-C25</f>
-        <v>422380.27</v>
+        <v>513425.48</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="77">
         <f>+C27</f>
-        <v>422380.27</v>
+        <v>513425.48</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="65">
         <f>+C27+C36</f>
-        <v>422380.27</v>
+        <v>513425.48</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="141"/>
-      <c r="C46" s="141"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="141"/>
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="139"/>
+      <c r="C46" s="139"/>
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="139"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="139"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -2413,25 +2423,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2452,7 +2462,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2468,11 +2478,11 @@
       <c r="H2" s="74"/>
       <c r="I2" s="74"/>
       <c r="J2" s="74"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2503,7 +2513,7 @@
       <c r="J3" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="115" t="s">
         <v>38</v>
       </c>
       <c r="L3" s="30" t="s">
@@ -2513,7 +2523,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2536,7 +2546,7 @@
       <c r="J4" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="117" t="s">
+      <c r="K4" s="116" t="s">
         <v>39</v>
       </c>
       <c r="L4" s="66" t="str">
@@ -2547,7 +2557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2559,19 +2569,16 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>70681.856</v>
-      </c>
-      <c r="F5" s="80">
-        <f>E5</f>
-        <v>70681.856</v>
-      </c>
+        <v>86036.752000000008</v>
+      </c>
+      <c r="F5" s="80"/>
       <c r="G5" s="67">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>86036.752000000008</v>
       </c>
       <c r="H5" s="70">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
+        <v>3441.4700800000005</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2580,20 +2587,20 @@
         <f>K$1/5</f>
         <v>86036.752000000008</v>
       </c>
-      <c r="K5" s="118">
+      <c r="K5" s="117">
         <f>K2*D5</f>
         <v>0</v>
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>86036.752000000008</v>
+        <v>175514.97408000001</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>89478.222080000007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>182535.57304320001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2605,11 +2612,11 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>159397.48559999999</v>
-      </c>
-      <c r="F6" s="80">
+        <v>86036.752000000008</v>
+      </c>
+      <c r="F6" s="172">
         <f>E6</f>
-        <v>159397.48559999999</v>
+        <v>86036.752000000008</v>
       </c>
       <c r="G6" s="67">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
@@ -2626,7 +2633,7 @@
         <f t="shared" ref="J6:J9" si="2">K$1/5</f>
         <v>86036.752000000008</v>
       </c>
-      <c r="K6" s="118">
+      <c r="K6" s="117">
         <f>K2*D6</f>
         <v>0</v>
       </c>
@@ -2639,7 +2646,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2651,16 +2658,16 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>70681.856</v>
+        <v>159545.88224000001</v>
       </c>
       <c r="F7" s="80"/>
       <c r="G7" s="67">
         <f t="shared" si="0"/>
-        <v>70681.856</v>
+        <v>159545.88224000001</v>
       </c>
       <c r="H7" s="70">
         <f t="shared" si="1"/>
-        <v>2827.2742400000002</v>
+        <v>6381.8352896000006</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2669,20 +2676,20 @@
         <f t="shared" si="2"/>
         <v>86036.752000000008</v>
       </c>
-      <c r="K7" s="118">
+      <c r="K7" s="117">
         <f>K2*D7</f>
         <v>0</v>
       </c>
       <c r="L7" s="15">
         <f t="shared" si="3"/>
-        <v>159545.88224000001</v>
+        <v>251964.4695296</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="4"/>
-        <v>165927.71752960002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>262043.04831078401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2694,18 +2701,16 @@
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>418239.95708031999</v>
-      </c>
-      <c r="F8" s="80">
-        <v>79432.09</v>
-      </c>
+        <v>438396.93376353284</v>
+      </c>
+      <c r="F8" s="80"/>
       <c r="G8" s="67">
         <f t="shared" si="0"/>
-        <v>338807.86708032002</v>
+        <v>438396.93376353284</v>
       </c>
       <c r="H8" s="70">
         <f t="shared" si="1"/>
-        <v>13552.3146832128</v>
+        <v>17535.877350541316</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -2714,20 +2719,20 @@
         <f t="shared" si="2"/>
         <v>86036.752000000008</v>
       </c>
-      <c r="K8" s="118">
+      <c r="K8" s="117">
         <f>K2*D8</f>
         <v>0</v>
       </c>
       <c r="L8" s="15">
         <f t="shared" si="3"/>
-        <v>438396.93376353284</v>
+        <v>541969.56311407418</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="4"/>
-        <v>455932.81111407414</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>563648.3456386372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2739,11 +2744,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>70681.856</v>
-      </c>
-      <c r="F9" s="80">
+        <v>86036.752000000008</v>
+      </c>
+      <c r="F9" s="172">
         <f>E9</f>
-        <v>70681.856</v>
+        <v>86036.752000000008</v>
       </c>
       <c r="G9" s="67">
         <f t="shared" si="0"/>
@@ -2760,7 +2765,7 @@
         <f t="shared" si="2"/>
         <v>86036.752000000008</v>
       </c>
-      <c r="K9" s="118">
+      <c r="K9" s="117">
         <f>K2*D9</f>
         <v>0</v>
       </c>
@@ -2773,7 +2778,7 @@
         <v>89478.222080000007</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2785,19 +2790,19 @@
       </c>
       <c r="E10" s="42">
         <f t="shared" si="5"/>
-        <v>789683.01068031997</v>
+        <v>856053.07200353278</v>
       </c>
       <c r="F10" s="42">
         <f t="shared" si="5"/>
-        <v>380193.28760000004</v>
+        <v>172073.50400000002</v>
       </c>
       <c r="G10" s="50">
         <f t="shared" si="5"/>
-        <v>409489.72308032005</v>
+        <v>683979.56800353283</v>
       </c>
       <c r="H10" s="50">
         <f t="shared" si="5"/>
-        <v>16379.588923212801</v>
+        <v>27359.182720141318</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="5"/>
@@ -2811,80 +2816,80 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L10" s="119">
+      <c r="L10" s="118">
         <f t="shared" si="5"/>
-        <v>856053.07200353278</v>
-      </c>
-      <c r="M10" s="119">
+        <v>1141522.5107236744</v>
+      </c>
+      <c r="M10" s="118">
         <f t="shared" si="5"/>
-        <v>890295.19488367415</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="142"/>
-      <c r="B11" s="142"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="142"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1187183.4111526213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="140"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="140"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="143"/>
-      <c r="L13" s="143"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="143"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="143"/>
-      <c r="K14" s="143"/>
-      <c r="L14" s="143"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="143"/>
-      <c r="I15" s="143"/>
-      <c r="J15" s="143"/>
-      <c r="K15" s="143"/>
-      <c r="L15" s="143"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="141"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="141"/>
+      <c r="H13" s="141"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="141"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="141"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="141"/>
+      <c r="I14" s="141"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="141"/>
+      <c r="L14" s="141"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2903,33 +2908,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1"/>
       <c r="B1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="B2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="B3"/>
       <c r="K3" t="s">
@@ -2937,18 +2942,18 @@
       </c>
       <c r="M3" s="6">
         <f>E6</f>
-        <v>154256.57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>63384.56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="139">
-        <v>172930.24</v>
+      <c r="D4" s="124"/>
+      <c r="E4" s="136">
+        <v>62811</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -2962,92 +2967,92 @@
       <c r="K4" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="121">
+      <c r="O4" s="120">
         <f>M3-K8</f>
-        <v>71763.12000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-19108.89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5" s="33" t="s">
         <v>74</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="170">
-        <v>47589.49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="137">
+        <v>79268.710000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6" s="108" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="108"/>
-      <c r="E6" s="136">
-        <v>154256.57</v>
-      </c>
-      <c r="G6" s="125">
+      <c r="E6" s="170">
+        <v>63384.56</v>
+      </c>
+      <c r="G6" s="124">
         <v>1</v>
       </c>
-      <c r="H6" s="125">
+      <c r="H6" s="124">
         <v>1</v>
       </c>
       <c r="I6" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="125" t="s">
+      <c r="J6" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="K6" s="121">
+      <c r="K6" s="120">
         <f>E4/2</f>
-        <v>86465.12</v>
-      </c>
-      <c r="L6" s="127">
+        <v>31405.5</v>
+      </c>
+      <c r="L6" s="126">
         <f>O$4/5</f>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N6" s="128">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N6" s="127">
         <f>SUM(K6:M6)</f>
-        <v>100817.74399999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>27583.722000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7"/>
       <c r="B7"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124">
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123">
         <f>SUM(E4:E6)</f>
-        <v>374776.3</v>
-      </c>
-      <c r="G7" s="126">
+        <v>205464.27000000002</v>
+      </c>
+      <c r="G7" s="125">
         <v>2</v>
       </c>
-      <c r="H7" s="126">
+      <c r="H7" s="125">
         <v>2</v>
       </c>
-      <c r="I7" s="126" t="s">
+      <c r="I7" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="126" t="s">
+      <c r="J7" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="121">
+      <c r="K7" s="120">
         <f>E5/2</f>
-        <v>23794.744999999999</v>
-      </c>
-      <c r="L7" s="127">
+        <v>39634.355000000003</v>
+      </c>
+      <c r="L7" s="126">
         <f>O$4/5</f>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N7" s="134">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N7" s="133">
         <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
-        <v>38147.368999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35812.577000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
       <c r="B8"/>
       <c r="G8">
@@ -3062,231 +3067,225 @@
       <c r="J8" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="121">
+      <c r="K8" s="120">
         <v>82493.45</v>
       </c>
-      <c r="L8" s="127">
+      <c r="L8" s="126">
         <f t="shared" ref="L8:L11" si="1">O$4/5</f>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N8" s="132">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N8" s="131">
         <f t="shared" si="0"/>
-        <v>96846.073999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>78671.671999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9"/>
-      <c r="G9" s="126">
+      <c r="G9" s="125">
         <v>4</v>
       </c>
-      <c r="H9" s="126">
+      <c r="H9" s="125">
         <v>4</v>
       </c>
-      <c r="I9" s="126" t="s">
+      <c r="I9" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="126" t="s">
+      <c r="J9" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="121">
+      <c r="K9" s="120">
         <f>E5/2</f>
-        <v>23794.744999999999</v>
-      </c>
-      <c r="L9" s="127">
+        <v>39634.355000000003</v>
+      </c>
+      <c r="L9" s="126">
         <f t="shared" si="1"/>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N9" s="134">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N9" s="133">
         <f t="shared" si="0"/>
-        <v>38147.368999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35812.577000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10"/>
       <c r="B10"/>
-      <c r="G10" s="125">
+      <c r="G10" s="124">
         <v>5</v>
       </c>
-      <c r="H10" s="125">
+      <c r="H10" s="124">
         <v>5</v>
       </c>
       <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="125" t="s">
+      <c r="J10" s="124" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="121">
+      <c r="K10" s="120">
         <f>E4/2</f>
-        <v>86465.12</v>
-      </c>
-      <c r="L10" s="127">
+        <v>31405.5</v>
+      </c>
+      <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N10" s="130">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N10" s="129">
         <f t="shared" si="0"/>
-        <v>100817.74399999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>27583.722000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="B11"/>
-      <c r="L11" s="127">
+      <c r="L11" s="126">
         <f t="shared" si="1"/>
-        <v>14352.624000000002</v>
-      </c>
-      <c r="N11" s="129"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-3821.7779999999998</v>
+      </c>
+      <c r="N11" s="128"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="B12"/>
-      <c r="N12" s="129"/>
-    </row>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N12" s="128"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13"/>
-      <c r="C13" s="133" t="s">
+      <c r="C13" s="132" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="133"/>
-      <c r="M13" s="133"/>
-      <c r="N13" s="129"/>
-    </row>
-    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="128"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
       <c r="B14"/>
-      <c r="N14" s="131">
+      <c r="N14" s="130">
         <f>SUM(N6:N13)</f>
-        <v>374776.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>205464.27000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="120" t="s">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="120" t="s">
+      <c r="E17" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="120" t="s">
+      <c r="F17" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="147" t="s">
+      <c r="H17" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="148"/>
-      <c r="J17" s="149"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="121">
-        <v>110347.016</v>
-      </c>
-      <c r="E18" s="6">
-        <f>C18</f>
-        <v>110347.016</v>
-      </c>
+      <c r="I17" s="146"/>
+      <c r="J17" s="147"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C18" s="120">
+        <v>199078.77000000002</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6">
         <f>N6</f>
-        <v>100817.74399999999</v>
-      </c>
-      <c r="H18" s="150">
+        <v>27583.722000000002</v>
+      </c>
+      <c r="H18" s="148">
         <f>C18-E18+F18</f>
-        <v>100817.74399999999</v>
-      </c>
-      <c r="I18" s="151"/>
-      <c r="J18" s="152"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="121">
-        <v>160567.91</v>
-      </c>
-      <c r="E19" s="6"/>
+        <v>226662.49200000003</v>
+      </c>
+      <c r="I18" s="149"/>
+      <c r="J18" s="150"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C19" s="120">
+        <v>131973.81400000001</v>
+      </c>
+      <c r="E19" s="171">
+        <f>C19</f>
+        <v>131973.81400000001</v>
+      </c>
       <c r="F19" s="6">
         <f>N7</f>
-        <v>38147.368999999999</v>
-      </c>
-      <c r="H19" s="150">
+        <v>35812.577000000005</v>
+      </c>
+      <c r="H19" s="148">
         <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
-        <v>198715.27900000001</v>
-      </c>
-      <c r="I19" s="151"/>
-      <c r="J19" s="152"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="121">
-        <v>110347.016</v>
-      </c>
-      <c r="E20" s="6">
-        <f>C20</f>
-        <v>110347.016</v>
-      </c>
+        <v>35812.577000000005</v>
+      </c>
+      <c r="I19" s="149"/>
+      <c r="J19" s="150"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C20" s="120">
+        <v>96846.073999999993</v>
+      </c>
+      <c r="E20" s="171"/>
       <c r="F20" s="6">
         <f t="shared" ref="F20:F22" si="3">N8</f>
-        <v>96846.073999999993</v>
-      </c>
-      <c r="H20" s="150">
+        <v>78671.671999999991</v>
+      </c>
+      <c r="H20" s="148">
         <f>C20-E20+F20</f>
-        <v>96846.073999999993</v>
-      </c>
-      <c r="I20" s="151"/>
-      <c r="J20" s="152"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="121">
-        <v>160567.91</v>
-      </c>
-      <c r="E21" s="6">
-        <f>C21</f>
-        <v>160567.91</v>
-      </c>
+        <v>175517.74599999998</v>
+      </c>
+      <c r="I20" s="149"/>
+      <c r="J20" s="150"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="120">
+        <v>131973.81400000001</v>
+      </c>
+      <c r="E21" s="171"/>
       <c r="F21" s="6">
         <f>N9</f>
-        <v>38147.368999999999</v>
-      </c>
-      <c r="H21" s="150">
+        <v>35812.577000000005</v>
+      </c>
+      <c r="H21" s="148">
         <f t="shared" si="2"/>
-        <v>38147.368999999999</v>
-      </c>
-      <c r="I21" s="151"/>
-      <c r="J21" s="152"/>
-    </row>
-    <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="121">
-        <v>110347.016</v>
-      </c>
-      <c r="E22" s="6">
+        <v>167786.391</v>
+      </c>
+      <c r="I21" s="149"/>
+      <c r="J21" s="150"/>
+    </row>
+    <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="120">
+        <v>88731.754000000001</v>
+      </c>
+      <c r="E22" s="171">
         <f>C22</f>
-        <v>110347.016</v>
+        <v>88731.754000000001</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="3"/>
-        <v>100817.74399999999</v>
-      </c>
-      <c r="H22" s="144">
+        <v>27583.722000000002</v>
+      </c>
+      <c r="H22" s="142">
         <f t="shared" si="2"/>
-        <v>100817.74399999999</v>
-      </c>
-      <c r="I22" s="145"/>
-      <c r="J22" s="146"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+        <v>27583.722000000002</v>
+      </c>
+      <c r="I22" s="143"/>
+      <c r="J22" s="144"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E24" s="6">
         <f>SUM(E18:E23)</f>
-        <v>491608.95800000004</v>
+        <v>220705.56800000003</v>
       </c>
     </row>
   </sheetData>
@@ -3307,7 +3306,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59F83D-EB65-4E23-8775-704ADF1A523E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3316,68 +3315,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="158" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="160"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="161" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="159" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="164">
+      <c r="B2" s="160"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="162">
         <v>565</v>
       </c>
-      <c r="E2" s="165"/>
+      <c r="E2" s="163"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="166" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="166" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="166" t="s">
+      <c r="C3" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="168" t="s">
+      <c r="D3" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="153" t="s">
+      <c r="E3" s="151" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="153" t="s">
+      <c r="F3" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="153" t="s">
+      <c r="G3" s="151" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="167"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="165"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -3400,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -3469,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -3492,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -3534,12 +3533,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="155"/>
-      <c r="B12" s="156"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="157"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="153"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="155"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F71CE4-17A0-40B9-AD22-2FC5EE1F4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AB6946-2D1D-4A66-9C9C-C6A0EAC93FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="93">
   <si>
     <t>UF</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t xml:space="preserve">FERRETERIA V&amp;A </t>
+  </si>
+  <si>
+    <t>ARBA - CUOTA 2</t>
   </si>
 </sst>
 </file>
@@ -317,7 +320,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,13 +421,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1271,7 +1267,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1483,17 +1479,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1572,11 +1560,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2022,18 +2014,18 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="138" t="s">
+      <c r="E11" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="138"/>
+      <c r="F11" s="130"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="169">
-        <v>80236.31</v>
+      <c r="C12" s="161">
+        <v>78921.33</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="56" t="s">
@@ -2048,7 +2040,7 @@
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="134">
+      <c r="C13" s="161">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2057,7 +2049,7 @@
       </c>
       <c r="F13" s="59">
         <f>'prorrateo '!F10</f>
-        <v>172073.50400000002</v>
+        <v>856053.07200353278</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2067,7 +2059,7 @@
       <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="172">
+      <c r="C14" s="80">
         <v>33600</v>
       </c>
       <c r="D14" s="5"/>
@@ -2076,14 +2068,14 @@
       </c>
       <c r="F14" s="59">
         <f>-(C37)</f>
-        <v>-513425.48</v>
+        <v>-518428.1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="135">
+      <c r="C15" s="160">
         <v>39299</v>
       </c>
       <c r="D15" s="5"/>
@@ -2099,7 +2091,7 @@
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="135">
+      <c r="C16" s="160">
         <v>70904.02</v>
       </c>
       <c r="D16" s="5"/>
@@ -2108,14 +2100,14 @@
       </c>
       <c r="F16" s="59">
         <f>EDESUR!E24</f>
-        <v>220705.56800000003</v>
+        <v>648604.22600000002</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="135">
+      <c r="C17" s="160">
         <v>20000</v>
       </c>
       <c r="D17" s="5"/>
@@ -2126,7 +2118,7 @@
       <c r="A18" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="168">
+      <c r="C18" s="160">
         <v>12287</v>
       </c>
       <c r="D18" s="5"/>
@@ -2134,8 +2126,12 @@
       <c r="F18" s="59"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="160">
+        <v>6317.6</v>
+      </c>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
       <c r="H19" s="122" t="s">
@@ -2147,14 +2143,14 @@
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>348412.33</v>
+        <v>353414.95</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="121">
         <f>SUM(F12:F19)</f>
-        <v>-1810262.6780000001</v>
+        <v>-703387.07199646719</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2171,7 +2167,7 @@
         <v>66</v>
       </c>
       <c r="B22" s="35"/>
-      <c r="C22" s="135">
+      <c r="C22" s="160">
         <f>65203*5%+65203</f>
         <v>68463.149999999994</v>
       </c>
@@ -2184,7 +2180,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="135">
+      <c r="C23" s="160">
         <v>40000</v>
       </c>
       <c r="D23" s="5"/>
@@ -2196,7 +2192,7 @@
         <v>90</v>
       </c>
       <c r="B24" s="35"/>
-      <c r="C24" s="135">
+      <c r="C24" s="160">
         <v>56550</v>
       </c>
       <c r="D24" s="5"/>
@@ -2234,7 +2230,7 @@
       <c r="B27" s="48"/>
       <c r="C27" s="49">
         <f>+C26+C20</f>
-        <v>513425.48</v>
+        <v>518428.1</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
@@ -2312,7 +2308,7 @@
       </c>
       <c r="C37" s="53">
         <f>C27-C25</f>
-        <v>513425.48</v>
+        <v>518428.1</v>
       </c>
       <c r="F37" s="6"/>
     </row>
@@ -2322,7 +2318,7 @@
       </c>
       <c r="C38" s="77">
         <f>+C27</f>
-        <v>513425.48</v>
+        <v>518428.1</v>
       </c>
       <c r="F38" s="6"/>
     </row>
@@ -2333,7 +2329,7 @@
       <c r="B39" s="64"/>
       <c r="C39" s="65">
         <f>+C27+C36</f>
-        <v>513425.48</v>
+        <v>518428.1</v>
       </c>
       <c r="E39" s="16"/>
     </row>
@@ -2345,22 +2341,22 @@
       <c r="E45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="139"/>
-      <c r="C46" s="139"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
+      <c r="B46" s="131"/>
+      <c r="C46" s="131"/>
+      <c r="D46" s="131"/>
+      <c r="E46" s="131"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="139"/>
-      <c r="C47" s="139"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
+      <c r="B47" s="131"/>
+      <c r="C47" s="131"/>
+      <c r="D47" s="131"/>
+      <c r="E47" s="131"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="139"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
+      <c r="B48" s="131"/>
+      <c r="C48" s="131"/>
+      <c r="D48" s="131"/>
+      <c r="E48" s="131"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
@@ -2457,7 +2453,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>430183.76</v>
+        <v>518428.1</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
@@ -2571,21 +2567,24 @@
       <c r="E5" s="41">
         <v>86036.752000000008</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="80">
+        <f>E5</f>
+        <v>86036.752000000008</v>
+      </c>
       <c r="G5" s="67">
         <f>E5-F5</f>
-        <v>86036.752000000008</v>
+        <v>0</v>
       </c>
       <c r="H5" s="70">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>3441.4700800000005</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2593,11 +2592,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>175514.97408000001</v>
+        <v>103685.62</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>182535.57304320001</v>
+        <v>107833.04479999999</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2614,7 +2613,7 @@
       <c r="E6" s="41">
         <v>86036.752000000008</v>
       </c>
-      <c r="F6" s="172">
+      <c r="F6" s="80">
         <f>E6</f>
         <v>86036.752000000008</v>
       </c>
@@ -2631,7 +2630,7 @@
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J9" si="2">K$1/5</f>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2639,11 +2638,11 @@
       </c>
       <c r="L6" s="15">
         <f t="shared" ref="L6:L9" si="3">J6+K6+H6+G6</f>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="4">L6*4%+L6</f>
-        <v>89478.222080000007</v>
+        <v>107833.04479999999</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2660,21 +2659,24 @@
       <c r="E7" s="41">
         <v>159545.88224000001</v>
       </c>
-      <c r="F7" s="80"/>
+      <c r="F7" s="80">
+        <f t="shared" ref="F7:F8" si="5">E7</f>
+        <v>159545.88224000001</v>
+      </c>
       <c r="G7" s="67">
         <f t="shared" si="0"/>
-        <v>159545.88224000001</v>
+        <v>0</v>
       </c>
       <c r="H7" s="70">
         <f t="shared" si="1"/>
-        <v>6381.8352896000006</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="38">
         <f t="shared" si="2"/>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2682,11 +2684,11 @@
       </c>
       <c r="L7" s="15">
         <f t="shared" si="3"/>
-        <v>251964.4695296</v>
+        <v>103685.62</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="4"/>
-        <v>262043.04831078401</v>
+        <v>107833.04479999999</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2703,21 +2705,24 @@
       <c r="E8" s="41">
         <v>438396.93376353284</v>
       </c>
-      <c r="F8" s="80"/>
+      <c r="F8" s="80">
+        <f t="shared" si="5"/>
+        <v>438396.93376353284</v>
+      </c>
       <c r="G8" s="67">
         <f t="shared" si="0"/>
-        <v>438396.93376353284</v>
+        <v>0</v>
       </c>
       <c r="H8" s="70">
         <f t="shared" si="1"/>
-        <v>17535.877350541316</v>
+        <v>0</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="38">
         <f t="shared" si="2"/>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2725,11 +2730,11 @@
       </c>
       <c r="L8" s="15">
         <f t="shared" si="3"/>
-        <v>541969.56311407418</v>
+        <v>103685.62</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="4"/>
-        <v>563648.3456386372</v>
+        <v>107833.04479999999</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2746,7 +2751,7 @@
       <c r="E9" s="41">
         <v>86036.752000000008</v>
       </c>
-      <c r="F9" s="172">
+      <c r="F9" s="80">
         <f>E9</f>
         <v>86036.752000000008</v>
       </c>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="J9" s="38">
         <f t="shared" si="2"/>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2771,11 +2776,11 @@
       </c>
       <c r="L9" s="15">
         <f t="shared" si="3"/>
-        <v>86036.752000000008</v>
+        <v>103685.62</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="4"/>
-        <v>89478.222080000007</v>
+        <v>107833.04479999999</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2785,111 +2790,111 @@
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="45">
-        <f t="shared" ref="D10:M10" si="5">SUM(D5:D9)</f>
+        <f t="shared" ref="D10:M10" si="6">SUM(D5:D9)</f>
         <v>0</v>
       </c>
       <c r="E10" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>856053.07200353278</v>
       </c>
       <c r="F10" s="42">
-        <f t="shared" si="5"/>
-        <v>172073.50400000002</v>
+        <f t="shared" si="6"/>
+        <v>856053.07200353278</v>
       </c>
       <c r="G10" s="50">
-        <f t="shared" si="5"/>
-        <v>683979.56800353283</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="H10" s="50">
-        <f t="shared" si="5"/>
-        <v>27359.182720141318</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f t="shared" si="5"/>
-        <v>430183.76</v>
+        <f t="shared" si="6"/>
+        <v>518428.1</v>
       </c>
       <c r="K10" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L10" s="118">
-        <f t="shared" si="5"/>
-        <v>1141522.5107236744</v>
+        <f t="shared" si="6"/>
+        <v>518428.1</v>
       </c>
       <c r="M10" s="118">
-        <f t="shared" si="5"/>
-        <v>1187183.4111526213</v>
+        <f t="shared" si="6"/>
+        <v>539165.22399999993</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="140"/>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="141"/>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2952,7 +2957,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="136">
+      <c r="E4" s="163">
         <v>62811</v>
       </c>
       <c r="G4" t="s">
@@ -2979,7 +2984,7 @@
         <v>74</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="137">
+      <c r="E5" s="164">
         <v>79268.710000000006</v>
       </c>
     </row>
@@ -2990,7 +2995,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="108"/>
-      <c r="E6" s="170">
+      <c r="E6" s="168">
         <v>63384.56</v>
       </c>
       <c r="G6" s="124">
@@ -3013,7 +3018,7 @@
         <f>O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N6" s="127">
+      <c r="N6" s="165">
         <f>SUM(K6:M6)</f>
         <v>27583.722000000002</v>
       </c>
@@ -3047,7 +3052,7 @@
         <f>O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N7" s="133">
+      <c r="N7" s="166">
         <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
         <v>35812.577000000005</v>
       </c>
@@ -3074,7 +3079,7 @@
         <f t="shared" ref="L8:L11" si="1">O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N8" s="131">
+      <c r="N8" s="166">
         <f t="shared" si="0"/>
         <v>78671.671999999991</v>
       </c>
@@ -3102,7 +3107,7 @@
         <f t="shared" si="1"/>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N9" s="133">
+      <c r="N9" s="166">
         <f t="shared" si="0"/>
         <v>35812.577000000005</v>
       </c>
@@ -3130,7 +3135,7 @@
         <f t="shared" si="1"/>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N10" s="129">
+      <c r="N10" s="167">
         <f t="shared" si="0"/>
         <v>27583.722000000002</v>
       </c>
@@ -3142,35 +3147,35 @@
         <f t="shared" si="1"/>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N11" s="128"/>
+      <c r="N11" s="127"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="B12"/>
-      <c r="N12" s="128"/>
+      <c r="N12" s="127"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13"/>
-      <c r="C13" s="132" t="s">
+      <c r="C13" s="129" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="127"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
       <c r="B14"/>
-      <c r="N14" s="130">
+      <c r="N14" s="128">
         <f>SUM(N6:N13)</f>
         <v>205464.27000000002</v>
       </c>
@@ -3190,33 +3195,36 @@
       <c r="F17" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="145" t="s">
+      <c r="H17" s="137" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="146"/>
-      <c r="J17" s="147"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="139"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="120">
         <v>199078.77000000002</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="162">
+        <f>C18</f>
+        <v>199078.77000000002</v>
+      </c>
       <c r="F18" s="6">
         <f>N6</f>
         <v>27583.722000000002</v>
       </c>
-      <c r="H18" s="148">
+      <c r="H18" s="140">
         <f>C18-E18+F18</f>
-        <v>226662.49200000003</v>
-      </c>
-      <c r="I18" s="149"/>
-      <c r="J18" s="150"/>
+        <v>27583.722000000002</v>
+      </c>
+      <c r="I18" s="141"/>
+      <c r="J18" s="142"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="120">
         <v>131973.81400000001</v>
       </c>
-      <c r="E19" s="171">
+      <c r="E19" s="162">
         <f>C19</f>
         <v>131973.81400000001</v>
       </c>
@@ -3224,68 +3232,74 @@
         <f>N7</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="H19" s="148">
+      <c r="H19" s="140">
         <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="I19" s="149"/>
-      <c r="J19" s="150"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="120">
         <v>96846.073999999993</v>
       </c>
-      <c r="E20" s="171"/>
+      <c r="E20" s="162">
+        <f t="shared" ref="E20:E21" si="3">C20</f>
+        <v>96846.073999999993</v>
+      </c>
       <c r="F20" s="6">
-        <f t="shared" ref="F20:F22" si="3">N8</f>
+        <f t="shared" ref="F20:F22" si="4">N8</f>
         <v>78671.671999999991</v>
       </c>
-      <c r="H20" s="148">
+      <c r="H20" s="140">
         <f>C20-E20+F20</f>
-        <v>175517.74599999998</v>
-      </c>
-      <c r="I20" s="149"/>
-      <c r="J20" s="150"/>
+        <v>78671.671999999991</v>
+      </c>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="120">
         <v>131973.81400000001</v>
       </c>
-      <c r="E21" s="171"/>
+      <c r="E21" s="162">
+        <f t="shared" si="3"/>
+        <v>131973.81400000001</v>
+      </c>
       <c r="F21" s="6">
         <f>N9</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="H21" s="148">
+      <c r="H21" s="140">
         <f t="shared" si="2"/>
-        <v>167786.391</v>
-      </c>
-      <c r="I21" s="149"/>
-      <c r="J21" s="150"/>
+        <v>35812.577000000005</v>
+      </c>
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
     </row>
     <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="120">
         <v>88731.754000000001</v>
       </c>
-      <c r="E22" s="171">
+      <c r="E22" s="162">
         <f>C22</f>
         <v>88731.754000000001</v>
       </c>
       <c r="F22" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27583.722000000002</v>
       </c>
-      <c r="H22" s="142">
+      <c r="H22" s="134">
         <f t="shared" si="2"/>
         <v>27583.722000000002</v>
       </c>
-      <c r="I22" s="143"/>
-      <c r="J22" s="144"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="136"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E24" s="6">
         <f>SUM(E18:E23)</f>
-        <v>220705.56800000003</v>
+        <v>648604.22600000002</v>
       </c>
     </row>
   </sheetData>
@@ -3321,60 +3335,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="158"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="150"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="162">
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="154">
         <v>565</v>
       </c>
-      <c r="E2" s="163"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="164" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="164" t="s">
+      <c r="A3" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="166" t="s">
+      <c r="D3" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="E3" s="143" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="F3" s="143" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="143" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="165"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="157"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -3534,11 +3548,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="153"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="154"/>
-      <c r="E12" s="155"/>
+      <c r="A12" s="145"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
+      <c r="E12" s="147"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
+++ b/PICHINCHA/Mayo/PICHINCHA-MAYO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AB6946-2D1D-4A66-9C9C-C6A0EAC93FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BF03F3-6F90-41BF-A55D-CECB5D3A1099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$A$1:$O$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
   <si>
     <t>UF</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>ARBA - CUOTA 2</t>
+  </si>
+  <si>
+    <t>SERVISUR - CAMBIO DE FOTCELULA - MANO DE OBRA Y MATERIAL</t>
   </si>
 </sst>
 </file>
@@ -1482,84 +1485,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1569,6 +1494,84 @@
     <xf numFmtId="164" fontId="10" fillId="6" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1936,7 +1939,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2014,17 +2017,17 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="130" t="s">
+      <c r="E11" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="130"/>
+      <c r="F11" s="139"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="161">
+      <c r="C12" s="131">
         <v>78921.33</v>
       </c>
       <c r="D12" s="5"/>
@@ -2040,7 +2043,7 @@
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="161">
+      <c r="C13" s="131">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2067,15 +2070,15 @@
         <v>20</v>
       </c>
       <c r="F14" s="59">
-        <f>-(C37)</f>
-        <v>-518428.1</v>
+        <f>-(C38)</f>
+        <v>-550928.1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="160">
+      <c r="C15" s="130">
         <v>39299</v>
       </c>
       <c r="D15" s="5"/>
@@ -2091,7 +2094,7 @@
       <c r="A16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="160">
+      <c r="C16" s="130">
         <v>70904.02</v>
       </c>
       <c r="D16" s="5"/>
@@ -2107,7 +2110,7 @@
       <c r="A17" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="160">
+      <c r="C17" s="130">
         <v>20000</v>
       </c>
       <c r="D17" s="5"/>
@@ -2118,7 +2121,7 @@
       <c r="A18" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="160">
+      <c r="C18" s="130">
         <v>12287</v>
       </c>
       <c r="D18" s="5"/>
@@ -2129,7 +2132,7 @@
       <c r="A19" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="160">
+      <c r="C19" s="130">
         <v>6317.6</v>
       </c>
       <c r="E19" s="58"/>
@@ -2150,7 +2153,7 @@
       </c>
       <c r="F20" s="121">
         <f>SUM(F12:F19)</f>
-        <v>-703387.07199646719</v>
+        <v>-735887.07199646719</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2167,7 +2170,7 @@
         <v>66</v>
       </c>
       <c r="B22" s="35"/>
-      <c r="C22" s="160">
+      <c r="C22" s="130">
         <f>65203*5%+65203</f>
         <v>68463.149999999994</v>
       </c>
@@ -2180,205 +2183,213 @@
         <v>89</v>
       </c>
       <c r="B23" s="35"/>
-      <c r="C23" s="160">
+      <c r="C23" s="130">
         <v>40000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B24" s="35"/>
-      <c r="C24" s="160">
-        <v>56550</v>
+      <c r="C24" s="130">
+        <f>25000+7500</f>
+        <v>32500</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B25" s="35"/>
-      <c r="C25" s="112">
-        <v>0</v>
+      <c r="C25" s="130">
+        <v>56550</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="109">
-        <f>SUM(C21:C25)</f>
-        <v>165013.15</v>
+      <c r="A26" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="112">
+        <v>0</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="6"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="109">
+        <f>SUM(C21:C26)</f>
+        <v>197513.15</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="49">
-        <f>+C26+C20</f>
-        <v>518428.1</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="82"/>
-      <c r="C28" s="83"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49">
+        <f>+C27+C20</f>
+        <v>550928.1</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="69" t="s">
         <v>24</v>
       </c>
+      <c r="B29" s="82"/>
+      <c r="C29" s="83"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="54"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="22" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="53">
-        <v>0</v>
-      </c>
+      <c r="A31" s="44"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="54"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
-      <c r="B32" s="62"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="51"/>
       <c r="C32" s="53">
         <v>0</v>
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="78"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="81"/>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="86"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="81"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="81">
-        <v>0</v>
-      </c>
+      <c r="B35" s="85"/>
+      <c r="C35" s="86"/>
       <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="63" t="s">
+      <c r="A36" s="78"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="81">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="65">
-        <f>SUM(C31:C35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" s="64"/>
+      <c r="C37" s="65">
+        <f>SUM(C32:C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="53">
-        <f>C27-C25</f>
-        <v>518428.1</v>
-      </c>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="C38" s="53">
+        <f>C28-C26</f>
+        <v>550928.1</v>
+      </c>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="77">
-        <f>+C27</f>
-        <v>518428.1</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="s">
+      <c r="C39" s="77">
+        <f>+C28</f>
+        <v>550928.1</v>
+      </c>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="65">
-        <f>+C27+C36</f>
-        <v>518428.1</v>
-      </c>
-      <c r="E39" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D44" s="6"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="65">
+        <f>+C28+C37</f>
+        <v>550928.1</v>
+      </c>
+      <c r="E40" s="16"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="6"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="131"/>
-      <c r="C46" s="131"/>
-      <c r="D46" s="131"/>
-      <c r="E46" s="131"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="131"/>
-      <c r="C47" s="131"/>
-      <c r="D47" s="131"/>
-      <c r="E47" s="131"/>
+      <c r="B47" s="140"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="131"/>
-      <c r="C48" s="131"/>
-      <c r="D48" s="131"/>
-      <c r="E48" s="131"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="19"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="20"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
+      <c r="B48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="140"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="19"/>
       <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="20"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -2398,10 +2409,15 @@
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B46:E48"/>
+    <mergeCell ref="B47:E49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2453,7 +2469,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>518428.1</v>
+        <v>550928.1</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
@@ -2584,7 +2600,7 @@
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2592,11 +2608,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>107833.04479999999</v>
+        <v>114593.04479999999</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2630,7 +2646,7 @@
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J9" si="2">K$1/5</f>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2638,11 +2654,11 @@
       </c>
       <c r="L6" s="15">
         <f t="shared" ref="L6:L9" si="3">J6+K6+H6+G6</f>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="4">L6*4%+L6</f>
-        <v>107833.04479999999</v>
+        <v>114593.04479999999</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2676,7 +2692,7 @@
       </c>
       <c r="J7" s="38">
         <f t="shared" si="2"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2684,11 +2700,11 @@
       </c>
       <c r="L7" s="15">
         <f t="shared" si="3"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="4"/>
-        <v>107833.04479999999</v>
+        <v>114593.04479999999</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2722,7 +2738,7 @@
       </c>
       <c r="J8" s="38">
         <f t="shared" si="2"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2730,11 +2746,11 @@
       </c>
       <c r="L8" s="15">
         <f t="shared" si="3"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="4"/>
-        <v>107833.04479999999</v>
+        <v>114593.04479999999</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2768,7 +2784,7 @@
       </c>
       <c r="J9" s="38">
         <f t="shared" si="2"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2776,11 +2792,11 @@
       </c>
       <c r="L9" s="15">
         <f t="shared" si="3"/>
-        <v>103685.62</v>
+        <v>110185.62</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="4"/>
-        <v>107833.04479999999</v>
+        <v>114593.04479999999</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2815,7 +2831,7 @@
       </c>
       <c r="J10" s="46">
         <f t="shared" si="6"/>
-        <v>518428.1</v>
+        <v>550928.1</v>
       </c>
       <c r="K10" s="46">
         <f t="shared" si="6"/>
@@ -2823,78 +2839,78 @@
       </c>
       <c r="L10" s="118">
         <f t="shared" si="6"/>
-        <v>518428.1</v>
+        <v>550928.1</v>
       </c>
       <c r="M10" s="118">
         <f t="shared" si="6"/>
-        <v>539165.22399999993</v>
+        <v>572965.22399999993</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
+      <c r="A11" s="141"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="133"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="133"/>
-      <c r="L14" s="133"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="133"/>
-      <c r="K16" s="133"/>
-      <c r="L16" s="133"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2957,7 +2973,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="163">
+      <c r="E4" s="133">
         <v>62811</v>
       </c>
       <c r="G4" t="s">
@@ -2984,7 +3000,7 @@
         <v>74</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="164">
+      <c r="E5" s="134">
         <v>79268.710000000006</v>
       </c>
     </row>
@@ -2995,7 +3011,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="108"/>
-      <c r="E6" s="168">
+      <c r="E6" s="138">
         <v>63384.56</v>
       </c>
       <c r="G6" s="124">
@@ -3018,7 +3034,7 @@
         <f>O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N6" s="165">
+      <c r="N6" s="135">
         <f>SUM(K6:M6)</f>
         <v>27583.722000000002</v>
       </c>
@@ -3052,7 +3068,7 @@
         <f>O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N7" s="166">
+      <c r="N7" s="136">
         <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
         <v>35812.577000000005</v>
       </c>
@@ -3079,7 +3095,7 @@
         <f t="shared" ref="L8:L11" si="1">O$4/5</f>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N8" s="166">
+      <c r="N8" s="136">
         <f t="shared" si="0"/>
         <v>78671.671999999991</v>
       </c>
@@ -3107,7 +3123,7 @@
         <f t="shared" si="1"/>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N9" s="166">
+      <c r="N9" s="136">
         <f t="shared" si="0"/>
         <v>35812.577000000005</v>
       </c>
@@ -3135,7 +3151,7 @@
         <f t="shared" si="1"/>
         <v>-3821.7779999999998</v>
       </c>
-      <c r="N10" s="167">
+      <c r="N10" s="137">
         <f t="shared" si="0"/>
         <v>27583.722000000002</v>
       </c>
@@ -3195,17 +3211,17 @@
       <c r="F17" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="137" t="s">
+      <c r="H17" s="146" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="138"/>
-      <c r="J17" s="139"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="148"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="120">
         <v>199078.77000000002</v>
       </c>
-      <c r="E18" s="162">
+      <c r="E18" s="132">
         <f>C18</f>
         <v>199078.77000000002</v>
       </c>
@@ -3213,18 +3229,18 @@
         <f>N6</f>
         <v>27583.722000000002</v>
       </c>
-      <c r="H18" s="140">
+      <c r="H18" s="149">
         <f>C18-E18+F18</f>
         <v>27583.722000000002</v>
       </c>
-      <c r="I18" s="141"/>
-      <c r="J18" s="142"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="151"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="120">
         <v>131973.81400000001</v>
       </c>
-      <c r="E19" s="162">
+      <c r="E19" s="132">
         <f>C19</f>
         <v>131973.81400000001</v>
       </c>
@@ -3232,18 +3248,18 @@
         <f>N7</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="H19" s="140">
+      <c r="H19" s="149">
         <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="I19" s="141"/>
-      <c r="J19" s="142"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="151"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="120">
         <v>96846.073999999993</v>
       </c>
-      <c r="E20" s="162">
+      <c r="E20" s="132">
         <f t="shared" ref="E20:E21" si="3">C20</f>
         <v>96846.073999999993</v>
       </c>
@@ -3251,18 +3267,18 @@
         <f t="shared" ref="F20:F22" si="4">N8</f>
         <v>78671.671999999991</v>
       </c>
-      <c r="H20" s="140">
+      <c r="H20" s="149">
         <f>C20-E20+F20</f>
         <v>78671.671999999991</v>
       </c>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="151"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="120">
         <v>131973.81400000001</v>
       </c>
-      <c r="E21" s="162">
+      <c r="E21" s="132">
         <f t="shared" si="3"/>
         <v>131973.81400000001</v>
       </c>
@@ -3270,18 +3286,18 @@
         <f>N9</f>
         <v>35812.577000000005</v>
       </c>
-      <c r="H21" s="140">
+      <c r="H21" s="149">
         <f t="shared" si="2"/>
         <v>35812.577000000005</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="I21" s="150"/>
+      <c r="J21" s="151"/>
     </row>
     <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="120">
         <v>88731.754000000001</v>
       </c>
-      <c r="E22" s="162">
+      <c r="E22" s="132">
         <f>C22</f>
         <v>88731.754000000001</v>
       </c>
@@ -3289,12 +3305,12 @@
         <f t="shared" si="4"/>
         <v>27583.722000000002</v>
       </c>
-      <c r="H22" s="134">
+      <c r="H22" s="143">
         <f t="shared" si="2"/>
         <v>27583.722000000002</v>
       </c>
-      <c r="I22" s="135"/>
-      <c r="J22" s="136"/>
+      <c r="I22" s="144"/>
+      <c r="J22" s="145"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E24" s="6">
@@ -3335,60 +3351,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="150"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="159"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="154">
+      <c r="B2" s="161"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="163">
         <v>565</v>
       </c>
-      <c r="E2" s="155"/>
+      <c r="E2" s="164"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="156" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="156" t="s">
+      <c r="A3" s="165" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="158" t="s">
+      <c r="D3" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="143" t="s">
+      <c r="E3" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="143" t="s">
+      <c r="F3" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="143" t="s">
+      <c r="G3" s="152" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="166"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -3548,11 +3564,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="145"/>
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="147"/>
+      <c r="A12" s="154"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="155"/>
+      <c r="E12" s="156"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>
